--- a/artfynd/Iksjak-Råssnesudden artfynd.xlsx
+++ b/artfynd/Iksjak-Råssnesudden artfynd.xlsx
@@ -15326,7 +15326,7 @@
         <v>135380389</v>
       </c>
       <c r="B128" t="n">
-        <v>83466</v>
+        <v>83468</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -15442,7 +15442,7 @@
         <v>135380390</v>
       </c>
       <c r="B129" t="n">
-        <v>83466</v>
+        <v>83468</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>

--- a/artfynd/Iksjak-Råssnesudden artfynd.xlsx
+++ b/artfynd/Iksjak-Råssnesudden artfynd.xlsx
@@ -15326,7 +15326,7 @@
         <v>135380389</v>
       </c>
       <c r="B128" t="n">
-        <v>83468</v>
+        <v>83472</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -15442,7 +15442,7 @@
         <v>135380390</v>
       </c>
       <c r="B129" t="n">
-        <v>83468</v>
+        <v>83472</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>

--- a/artfynd/Iksjak-Råssnesudden artfynd.xlsx
+++ b/artfynd/Iksjak-Råssnesudden artfynd.xlsx
@@ -15326,7 +15326,7 @@
         <v>135380389</v>
       </c>
       <c r="B128" t="n">
-        <v>83472</v>
+        <v>83474</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -15442,7 +15442,7 @@
         <v>135380390</v>
       </c>
       <c r="B129" t="n">
-        <v>83472</v>
+        <v>83474</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>

--- a/artfynd/Iksjak-Råssnesudden artfynd.xlsx
+++ b/artfynd/Iksjak-Råssnesudden artfynd.xlsx
@@ -15326,7 +15326,7 @@
         <v>135380389</v>
       </c>
       <c r="B128" t="n">
-        <v>83474</v>
+        <v>83475</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -15442,7 +15442,7 @@
         <v>135380390</v>
       </c>
       <c r="B129" t="n">
-        <v>83474</v>
+        <v>83475</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>

--- a/artfynd/Iksjak-Råssnesudden artfynd.xlsx
+++ b/artfynd/Iksjak-Råssnesudden artfynd.xlsx
@@ -6985,7 +6985,7 @@
         <v>135388781</v>
       </c>
       <c r="B56" t="n">
-        <v>58899</v>
+        <v>58903</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7102,7 +7102,7 @@
         <v>135388782</v>
       </c>
       <c r="B57" t="n">
-        <v>58899</v>
+        <v>58903</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7219,7 +7219,7 @@
         <v>135388780</v>
       </c>
       <c r="B58" t="n">
-        <v>80106</v>
+        <v>80111</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -11152,7 +11152,7 @@
         <v>135388775</v>
       </c>
       <c r="B92" t="n">
-        <v>78919</v>
+        <v>78924</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11268,7 +11268,7 @@
         <v>135388777</v>
       </c>
       <c r="B93" t="n">
-        <v>78919</v>
+        <v>78924</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11384,7 +11384,7 @@
         <v>135388778</v>
       </c>
       <c r="B94" t="n">
-        <v>78919</v>
+        <v>78924</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11858,7 +11858,7 @@
         <v>135388772</v>
       </c>
       <c r="B98" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11984,7 +11984,7 @@
         <v>135388774</v>
       </c>
       <c r="B99" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -14918,7 +14918,7 @@
         <v>135388773</v>
       </c>
       <c r="B124" t="n">
-        <v>80106</v>
+        <v>80111</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -15044,7 +15044,7 @@
         <v>135388776</v>
       </c>
       <c r="B125" t="n">
-        <v>80106</v>
+        <v>80111</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -15170,7 +15170,7 @@
         <v>135388783</v>
       </c>
       <c r="B126" t="n">
-        <v>79539</v>
+        <v>79544</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -22577,7 +22577,7 @@
         <v>135388784</v>
       </c>
       <c r="B190" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -22694,7 +22694,7 @@
         <v>135388785</v>
       </c>
       <c r="B191" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>

--- a/artfynd/Iksjak-Råssnesudden artfynd.xlsx
+++ b/artfynd/Iksjak-Råssnesudden artfynd.xlsx
@@ -7219,7 +7219,7 @@
         <v>135388780</v>
       </c>
       <c r="B58" t="n">
-        <v>80111</v>
+        <v>80122</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -11152,7 +11152,7 @@
         <v>135388775</v>
       </c>
       <c r="B92" t="n">
-        <v>78924</v>
+        <v>78935</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11268,7 +11268,7 @@
         <v>135388777</v>
       </c>
       <c r="B93" t="n">
-        <v>78924</v>
+        <v>78935</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11384,7 +11384,7 @@
         <v>135388778</v>
       </c>
       <c r="B94" t="n">
-        <v>78924</v>
+        <v>78935</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11858,7 +11858,7 @@
         <v>135388772</v>
       </c>
       <c r="B98" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11984,7 +11984,7 @@
         <v>135388774</v>
       </c>
       <c r="B99" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -14918,7 +14918,7 @@
         <v>135388773</v>
       </c>
       <c r="B124" t="n">
-        <v>80111</v>
+        <v>80122</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -15044,7 +15044,7 @@
         <v>135388776</v>
       </c>
       <c r="B125" t="n">
-        <v>80111</v>
+        <v>80122</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -15170,7 +15170,7 @@
         <v>135388783</v>
       </c>
       <c r="B126" t="n">
-        <v>79544</v>
+        <v>79555</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>

--- a/artfynd/Iksjak-Råssnesudden artfynd.xlsx
+++ b/artfynd/Iksjak-Råssnesudden artfynd.xlsx
@@ -7219,7 +7219,7 @@
         <v>135388780</v>
       </c>
       <c r="B58" t="n">
-        <v>80122</v>
+        <v>80123</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -11152,7 +11152,7 @@
         <v>135388775</v>
       </c>
       <c r="B92" t="n">
-        <v>78935</v>
+        <v>78936</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11268,7 +11268,7 @@
         <v>135388777</v>
       </c>
       <c r="B93" t="n">
-        <v>78935</v>
+        <v>78936</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11384,7 +11384,7 @@
         <v>135388778</v>
       </c>
       <c r="B94" t="n">
-        <v>78935</v>
+        <v>78936</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11858,7 +11858,7 @@
         <v>135388772</v>
       </c>
       <c r="B98" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11984,7 +11984,7 @@
         <v>135388774</v>
       </c>
       <c r="B99" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -14918,7 +14918,7 @@
         <v>135388773</v>
       </c>
       <c r="B124" t="n">
-        <v>80122</v>
+        <v>80123</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -15044,7 +15044,7 @@
         <v>135388776</v>
       </c>
       <c r="B125" t="n">
-        <v>80122</v>
+        <v>80123</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -15170,7 +15170,7 @@
         <v>135388783</v>
       </c>
       <c r="B126" t="n">
-        <v>79555</v>
+        <v>79556</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>

--- a/artfynd/Iksjak-Råssnesudden artfynd.xlsx
+++ b/artfynd/Iksjak-Råssnesudden artfynd.xlsx
@@ -7219,7 +7219,7 @@
         <v>135388780</v>
       </c>
       <c r="B58" t="n">
-        <v>80123</v>
+        <v>80125</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -11152,7 +11152,7 @@
         <v>135388775</v>
       </c>
       <c r="B92" t="n">
-        <v>78936</v>
+        <v>78938</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11268,7 +11268,7 @@
         <v>135388777</v>
       </c>
       <c r="B93" t="n">
-        <v>78936</v>
+        <v>78938</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11384,7 +11384,7 @@
         <v>135388778</v>
       </c>
       <c r="B94" t="n">
-        <v>78936</v>
+        <v>78938</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11858,7 +11858,7 @@
         <v>135388772</v>
       </c>
       <c r="B98" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11984,7 +11984,7 @@
         <v>135388774</v>
       </c>
       <c r="B99" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -14918,7 +14918,7 @@
         <v>135388773</v>
       </c>
       <c r="B124" t="n">
-        <v>80123</v>
+        <v>80125</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -15044,7 +15044,7 @@
         <v>135388776</v>
       </c>
       <c r="B125" t="n">
-        <v>80123</v>
+        <v>80125</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -15170,7 +15170,7 @@
         <v>135388783</v>
       </c>
       <c r="B126" t="n">
-        <v>79556</v>
+        <v>79558</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>

--- a/artfynd/Iksjak-Råssnesudden artfynd.xlsx
+++ b/artfynd/Iksjak-Råssnesudden artfynd.xlsx
@@ -6985,7 +6985,7 @@
         <v>135388781</v>
       </c>
       <c r="B56" t="n">
-        <v>58903</v>
+        <v>58906</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7102,7 +7102,7 @@
         <v>135388782</v>
       </c>
       <c r="B57" t="n">
-        <v>58903</v>
+        <v>58906</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7219,7 +7219,7 @@
         <v>135388780</v>
       </c>
       <c r="B58" t="n">
-        <v>80125</v>
+        <v>80129</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -11152,7 +11152,7 @@
         <v>135388775</v>
       </c>
       <c r="B92" t="n">
-        <v>78938</v>
+        <v>78942</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11268,7 +11268,7 @@
         <v>135388777</v>
       </c>
       <c r="B93" t="n">
-        <v>78938</v>
+        <v>78942</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11384,7 +11384,7 @@
         <v>135388778</v>
       </c>
       <c r="B94" t="n">
-        <v>78938</v>
+        <v>78942</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11858,7 +11858,7 @@
         <v>135388772</v>
       </c>
       <c r="B98" t="n">
-        <v>80154</v>
+        <v>80158</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11984,7 +11984,7 @@
         <v>135388774</v>
       </c>
       <c r="B99" t="n">
-        <v>80154</v>
+        <v>80158</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -14918,7 +14918,7 @@
         <v>135388773</v>
       </c>
       <c r="B124" t="n">
-        <v>80125</v>
+        <v>80129</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -15044,7 +15044,7 @@
         <v>135388776</v>
       </c>
       <c r="B125" t="n">
-        <v>80125</v>
+        <v>80129</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -15170,7 +15170,7 @@
         <v>135388783</v>
       </c>
       <c r="B126" t="n">
-        <v>79558</v>
+        <v>79562</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -22577,7 +22577,7 @@
         <v>135388784</v>
       </c>
       <c r="B190" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -22694,7 +22694,7 @@
         <v>135388785</v>
       </c>
       <c r="B191" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
